--- a/templates/gworkspace/deccan-workbook-for-drive.xlsx
+++ b/templates/gworkspace/deccan-workbook-for-drive.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="0"/>
   <fonts count="5">
     <font>
-      <name val="Calibri"/>
+      <name val="Segoe UI Variable Text"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -224,112 +224,54 @@
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Deccan">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="1C1917"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44403C"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="F5F5F4"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="164999"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="2D5BA3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="7392C2"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="B9C8E0"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="DCE4F0"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="78716C"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="164999"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="7392C2"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Deccan">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Segoe UI Variable Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Segoe UI Variable Text"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -542,66 +484,70 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n"/>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
+      <c r="A4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
+      <c r="A5" s="3" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n"/>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
+      <c r="A7" s="3" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n"/>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
+      <c r="A9" s="3" t="inlineStr"/>
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n"/>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n"/>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
+      <c r="A11" s="3" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;"Cascadia Mono,Regular"&amp;9&amp;K78716CDeccan Fine Chemicals · Confidential&amp;R&amp;"Cascadia Mono,Regular"&amp;9&amp;K78716C&amp;P</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>